--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0127.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0127.xlsx
@@ -11825,7 +11825,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Giờ thì r?i ?i. Hẹn gặp lại.</t>
+          <t>Giờ thì Rời đi. Hẹn gặp lại.</t>
         </is>
       </c>
     </row>
@@ -21349,7 +21349,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>R?i ?i ngay!</t>
+          <t>Rời đi ngay!</t>
         </is>
       </c>
     </row>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>R?i ?i ngay... l?p t?c!</t>
+          <t>Rời đi ngay... lập tức!</t>
         </is>
       </c>
     </row>
